--- a/RESULTS/tables/threshold_tradeoff_external_hybridxgbrf.xlsx
+++ b/RESULTS/tables/threshold_tradeoff_external_hybridxgbrf.xlsx
@@ -515,49 +515,49 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2342342342342342</v>
+        <v>0.2338946088946089</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6208172458172458</v>
+        <v>0.6782496782496783</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4279279279279279</v>
+        <v>0.4691114245416079</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9601347557551937</v>
+        <v>0.9337450870297586</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9601347557551937</v>
+        <v>0.9337450870297586</v>
       </c>
       <c r="G2" t="n">
-        <v>0.484554678692221</v>
+        <v>0.5756482525366403</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4279279279279279</v>
+        <v>0.4691114245416079</v>
       </c>
       <c r="I2" t="n">
-        <v>0.968018018018018</v>
+        <v>0.9558217895919131</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5920027696036004</v>
+        <v>0.6244836650394292</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8867580061870668</v>
+        <v>0.8976695635440358</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1215904813632756</v>
+        <v>0.1122090732378589</v>
       </c>
       <c r="M2" t="n">
-        <v>1710</v>
+        <v>1663</v>
       </c>
       <c r="N2" t="n">
-        <v>2286</v>
+        <v>1882</v>
       </c>
       <c r="O2" t="n">
-        <v>2149</v>
+        <v>2553</v>
       </c>
       <c r="P2" t="n">
-        <v>71</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3">
@@ -565,49 +565,49 @@
         <v>0.2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1946187258687259</v>
+        <v>0.2013352638352638</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7665701415701416</v>
+        <v>0.778957528957529</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5616591928251121</v>
+        <v>0.5765325310267018</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8439079169006176</v>
+        <v>0.8607523862998315</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8439079169006176</v>
+        <v>0.8607523862998315</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7355129650507328</v>
+        <v>0.7461104847801578</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5616591928251121</v>
+        <v>0.5765325310267018</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9214689265536723</v>
+        <v>0.9302783244307</v>
       </c>
       <c r="J3" t="n">
-        <v>0.674444693740184</v>
+        <v>0.6905405405405406</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8867580061870668</v>
+        <v>0.8976695635440358</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1215904813632756</v>
+        <v>0.1122090732378589</v>
       </c>
       <c r="M3" t="n">
-        <v>1503</v>
+        <v>1533</v>
       </c>
       <c r="N3" t="n">
-        <v>1173</v>
+        <v>1126</v>
       </c>
       <c r="O3" t="n">
-        <v>3262</v>
+        <v>3309</v>
       </c>
       <c r="P3" t="n">
-        <v>278</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4">
@@ -615,49 +615,49 @@
         <v>0.3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1672412208126494</v>
+        <v>0.1716997609854753</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8227155727155727</v>
+        <v>0.8378378378378378</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6749098402885111</v>
+        <v>0.7143649473100389</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7355418304323413</v>
+        <v>0.7231892195395845</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7355418304323413</v>
+        <v>0.7231892195395845</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8577226606538895</v>
+        <v>0.8838782412626832</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6749098402885111</v>
+        <v>0.7143649473100389</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8898245614035087</v>
+        <v>0.8882846136415137</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7039226222461042</v>
+        <v>0.71875</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8867580061870668</v>
+        <v>0.8976695635440358</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1215904813632756</v>
+        <v>0.1122090732378589</v>
       </c>
       <c r="M4" t="n">
-        <v>1310</v>
+        <v>1288</v>
       </c>
       <c r="N4" t="n">
-        <v>631</v>
+        <v>515</v>
       </c>
       <c r="O4" t="n">
-        <v>3804</v>
+        <v>3920</v>
       </c>
       <c r="P4" t="n">
-        <v>471</v>
+        <v>493</v>
       </c>
     </row>
     <row r="5">
@@ -665,49 +665,49 @@
         <v>0.4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1397468897468898</v>
+        <v>0.1533676533676534</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8359073359073359</v>
+        <v>0.8516731016731016</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7704335465529495</v>
+        <v>0.8014035087719298</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6086468276249298</v>
+        <v>0.6412128017967434</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6086468276249298</v>
+        <v>0.6412128017967434</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9271702367531003</v>
+        <v>0.9361894024802706</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7704335465529495</v>
+        <v>0.8014035087719298</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8550634227490123</v>
+        <v>0.8666249217282405</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6800501882057717</v>
+        <v>0.7124142233312539</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8867580061870668</v>
+        <v>0.8976695635440358</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1215904813632756</v>
+        <v>0.1122090732378589</v>
       </c>
       <c r="M5" t="n">
-        <v>1084</v>
+        <v>1142</v>
       </c>
       <c r="N5" t="n">
-        <v>323</v>
+        <v>283</v>
       </c>
       <c r="O5" t="n">
-        <v>4112</v>
+        <v>4152</v>
       </c>
       <c r="P5" t="n">
-        <v>697</v>
+        <v>639</v>
       </c>
     </row>
     <row r="6">
@@ -715,49 +715,49 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1148648648648649</v>
+        <v>0.13497425997426</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8283462033462033</v>
+        <v>0.8484555984555985</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8562874251497006</v>
+        <v>0.8552074513124471</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4817518248175183</v>
+        <v>0.5670971364402021</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4817518248175183</v>
+        <v>0.5670971364402021</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9675310033821871</v>
+        <v>0.9614430665163473</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8562874251497006</v>
+        <v>0.8552074513124471</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8229766014576141</v>
+        <v>0.8468718967229394</v>
       </c>
       <c r="J6" t="n">
-        <v>0.616600790513834</v>
+        <v>0.6819716407832546</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8867580061870668</v>
+        <v>0.8976695635440358</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1215904813632756</v>
+        <v>0.1122090732378589</v>
       </c>
       <c r="M6" t="n">
-        <v>858</v>
+        <v>1010</v>
       </c>
       <c r="N6" t="n">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="O6" t="n">
-        <v>4291</v>
+        <v>4264</v>
       </c>
       <c r="P6" t="n">
-        <v>923</v>
+        <v>771</v>
       </c>
     </row>
   </sheetData>

--- a/RESULTS/tables/threshold_tradeoff_external_hybridxgbrf.xlsx
+++ b/RESULTS/tables/threshold_tradeoff_external_hybridxgbrf.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,82 +417,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Net Benefit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Sensitivity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Specificity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>PPV</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>NPV</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AUROC</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Brier</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
